--- a/Thor Allergy Tracker.xlsx
+++ b/Thor Allergy Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/F0F1021EA601D6BB/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{0FA1E62A-714A-4A3E-BDB6-E8F63FDB8898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDD2AFF9-E447-4CAF-BB6C-30AA68EFA8C9}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{0FA1E62A-714A-4A3E-BDB6-E8F63FDB8898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B01F2AF9-0EFE-4AEC-A5C4-B065D8241FF8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vet Report" sheetId="1" r:id="rId1"/>
@@ -40,15 +40,34 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="190">
   <si>
     <t>THOR'S ALLERGY &amp; SKIN REPORT</t>
   </si>
   <si>
-    <t>Observed patterns to support veterinary decisions — not a diagnosis.</t>
-  </si>
-  <si>
     <t>CURRENT TREATMENT PLAN</t>
   </si>
   <si>
@@ -127,9 +146,6 @@
     <t>Before injection</t>
   </si>
   <si>
-    <t>Week 1</t>
-  </si>
-  <si>
     <t>Week 2</t>
   </si>
   <si>
@@ -142,15 +158,6 @@
     <t>Weeks 5–8</t>
   </si>
   <si>
-    <t>Weeks 9–13</t>
-  </si>
-  <si>
-    <t>INTERPRETATION GUIDE</t>
-  </si>
-  <si>
-    <t>Look for patterns rather than proof of cause: whether symptoms change after an intervention, whether improvement fades as time since an injection increases, and whether food, grooming, stress, season, or unusual exposure overlap with symptom changes.</t>
-  </si>
-  <si>
     <t>DAILY CHECK IN — routine entry should take only a few minutes</t>
   </si>
   <si>
@@ -596,17 +603,48 @@
   </si>
   <si>
     <t>Hike at Lost Creek Lake</t>
+  </si>
+  <si>
+    <t>Ear areas are now dime sized, head shaking appears less.  Still licking paws often with a little redness in the webbed areas</t>
+  </si>
+  <si>
+    <t>Hike at Touvelle State Park</t>
+  </si>
+  <si>
+    <t>Thor was anxious all day, no real catalyst</t>
+  </si>
+  <si>
+    <t>Regular 16 week schedule</t>
+  </si>
+  <si>
+    <t>Weeks 1</t>
+  </si>
+  <si>
+    <t>Weeks 13-16</t>
+  </si>
+  <si>
+    <t>Weeks 9–12</t>
+  </si>
+  <si>
+    <t>Anxiety Medication</t>
+  </si>
+  <si>
+    <t>Fluoxetine 10 MG</t>
+  </si>
+  <si>
+    <t>Nutri-Vet Omega-3 Coat Care Fish Oil Softgels for Dogs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -646,8 +684,12 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -669,6 +711,12 @@
         <fgColor rgb="FFF8F7F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -682,7 +730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -703,17 +751,14 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -722,6 +767,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,10 +992,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="22.25" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
@@ -948,37 +1006,35 @@
     <col min="12" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:12" ht="23.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" ht="14.5">
-      <c r="A2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="3"/>
@@ -994,135 +1050,135 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:12" ht="15">
+      <c r="A4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="1:12" ht="15">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="56">
-      <c r="A6" s="3" t="str">
-        <f>'Treatment Plan'!B2</f>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="18" t="str" cm="1">
+        <f t="array" aca="1" ref="A6:F12" ca="1">_xlfn._xlws.FILTER('Treatment Plan'!B2:G100,(('Treatment Plan'!G2:G100="Active")+(('Treatment Plan'!E2:E100&gt;=TODAY()-30)*('Treatment Plan'!E2:E100&lt;=TODAY())))&gt;0,"")</f>
         <v>Purina Pro Plan Sensitive Skin &amp; Stomach Salmon Adult</v>
       </c>
       <c r="B6" s="3" t="str">
-        <f>'Treatment Plan'!C2</f>
+        <f ca="1"/>
         <v>Continuous Diet</v>
       </c>
-      <c r="C6" s="4">
-        <f>'Treatment Plan'!D2</f>
+      <c r="C6" s="17">
+        <f ca="1"/>
         <v>45992</v>
       </c>
-      <c r="D6" s="4">
-        <f ca="1">'Treatment Plan'!E2</f>
-        <v>46294</v>
-      </c>
-      <c r="E6" s="4">
-        <f ca="1">'Treatment Plan'!F2</f>
-        <v>46295</v>
+      <c r="D6" s="17">
+        <f ca="1"/>
+        <v>46302</v>
+      </c>
+      <c r="E6" s="17">
+        <f ca="1"/>
+        <v>46303</v>
       </c>
       <c r="F6" s="3" t="str">
-        <f>'Treatment Plan'!G2</f>
+        <f ca="1"/>
         <v>Active</v>
       </c>
       <c r="G6" s="6">
         <f ca="1">IFERROR(AVERAGEIFS('Daily Check In'!$B$5:$B$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;TODAY()-30),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" s="6">
         <f ca="1">IFERROR(AVERAGEIFS('Daily Check In'!$C$5:$C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;TODAY()-30),"")</f>
-        <v>3</v>
+        <v>2.1818181818181817</v>
       </c>
       <c r="I6" s="6">
         <f ca="1">IFERROR(AVERAGEIFS('Daily Check In'!$D$5:$D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;TODAY()-30),"")</f>
-        <v>3.5</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="J6" s="6">
         <f ca="1">IFERROR(AVERAGEIFS('Daily Check In'!$E$5:$E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;TODAY()-30),"")</f>
-        <v>4.75</v>
+        <v>3.0909090909090908</v>
       </c>
       <c r="K6" s="6">
         <f ca="1">IFERROR(AVERAGEIFS('Daily Check In'!$F$5:$F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;TODAY()-30),"")</f>
-        <v>2</v>
+        <v>1.8181818181818181</v>
       </c>
       <c r="L6" s="6">
         <f ca="1">IFERROR(AVERAGEIFS('Daily Check In'!$G$5:$G$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;TODAY()-30),"")</f>
-        <v>1.5</v>
+        <v>1.7272727272727273</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="3" t="str">
-        <f>'Treatment Plan'!B3</f>
+      <c r="A7" s="18" t="str">
+        <f ca="1"/>
         <v>Apoquel</v>
       </c>
       <c r="B7" s="3" t="str">
-        <f>'Treatment Plan'!C3</f>
+        <f ca="1"/>
         <v>Daily</v>
       </c>
-      <c r="C7" s="4">
-        <f>'Treatment Plan'!D3</f>
+      <c r="C7" s="17">
+        <f ca="1"/>
         <v>46013</v>
       </c>
-      <c r="D7" s="4">
-        <f ca="1">'Treatment Plan'!E3</f>
-        <v>46294</v>
-      </c>
-      <c r="E7" s="4">
-        <f ca="1">'Treatment Plan'!F3</f>
-        <v>46295</v>
+      <c r="D7" s="17">
+        <f ca="1"/>
+        <v>46302</v>
+      </c>
+      <c r="E7" s="17">
+        <f ca="1"/>
+        <v>46303</v>
       </c>
       <c r="F7" s="3" t="str">
-        <f>'Treatment Plan'!G3</f>
+        <f ca="1"/>
         <v>Active</v>
       </c>
       <c r="G7" s="3"/>
@@ -1132,157 +1188,157 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3" t="str">
-        <f>'Treatment Plan'!B4</f>
+    <row r="8" spans="1:12" ht="15">
+      <c r="A8" s="18" t="str">
+        <f ca="1"/>
         <v>Cytopoint</v>
       </c>
       <c r="B8" s="3" t="str">
-        <f>'Treatment Plan'!C4</f>
+        <f ca="1"/>
         <v>Every 4 months</v>
       </c>
-      <c r="C8" s="4">
-        <f>'Treatment Plan'!D4</f>
+      <c r="C8" s="17">
+        <f ca="1"/>
         <v>46037</v>
       </c>
-      <c r="D8" s="4">
-        <f>'Treatment Plan'!E4</f>
+      <c r="D8" s="17">
+        <f ca="1"/>
         <v>46181</v>
       </c>
-      <c r="E8" s="4">
-        <f>'Treatment Plan'!F4</f>
+      <c r="E8" s="17">
+        <f ca="1"/>
         <v>46303</v>
       </c>
       <c r="F8" s="3" t="str">
-        <f>'Treatment Plan'!G4</f>
+        <f ca="1"/>
         <v>Active</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="1:12" ht="15">
+      <c r="A9" s="18" t="str">
+        <f ca="1"/>
+        <v>Simparica Trio</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <f ca="1"/>
+        <v>Monthly on the 1st</v>
+      </c>
+      <c r="C9" s="17">
+        <f ca="1"/>
+        <v>44531</v>
+      </c>
+      <c r="D9" s="17">
+        <f ca="1"/>
+        <v>46296</v>
+      </c>
+      <c r="E9" s="17">
+        <f ca="1"/>
+        <v>46327</v>
+      </c>
+      <c r="F9" s="3" t="str">
+        <f ca="1"/>
+        <v>Active</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-    </row>
-    <row r="9" spans="1:12" ht="28">
-      <c r="A9" s="3" t="str">
-        <f>'Treatment Plan'!B5</f>
-        <v>Nordic Naturals Omega 3 Pet</v>
-      </c>
-      <c r="B9" s="3" t="str">
-        <f>'Treatment Plan'!C5</f>
-        <v>Daily</v>
-      </c>
-      <c r="C9" s="4">
-        <f>'Treatment Plan'!D5</f>
-        <v>46023</v>
-      </c>
-      <c r="D9" s="4">
-        <f ca="1">'Treatment Plan'!E5</f>
-        <v>46294</v>
-      </c>
-      <c r="E9" s="4">
-        <f ca="1">'Treatment Plan'!F5</f>
-        <v>46295</v>
-      </c>
-      <c r="F9" s="3" t="str">
-        <f>'Treatment Plan'!G5</f>
-        <v>Active</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="K9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="3" t="str">
-        <f>'Treatment Plan'!B6</f>
-        <v>Simparica Trio</v>
+      <c r="A10" s="18" t="str">
+        <f ca="1"/>
+        <v>Full grooming</v>
       </c>
       <c r="B10" s="3" t="str">
-        <f>'Treatment Plan'!C6</f>
-        <v>Monthly on the 1st</v>
-      </c>
-      <c r="C10" s="4">
-        <f>'Treatment Plan'!D6</f>
-        <v>44531</v>
-      </c>
-      <c r="D10" s="4">
-        <f>'Treatment Plan'!E6</f>
-        <v>46266</v>
-      </c>
-      <c r="E10" s="4">
-        <f>'Treatment Plan'!F6</f>
-        <v>46296</v>
+        <f ca="1"/>
+        <v>Every 4 Weeks</v>
+      </c>
+      <c r="C10" s="17">
+        <f ca="1"/>
+        <v>45511</v>
+      </c>
+      <c r="D10" s="17">
+        <f ca="1"/>
+        <v>46291</v>
+      </c>
+      <c r="E10" s="17">
+        <f ca="1"/>
+        <v>46319</v>
       </c>
       <c r="F10" s="3" t="str">
-        <f>'Treatment Plan'!G6</f>
+        <f ca="1"/>
         <v>Active</v>
       </c>
       <c r="G10" s="3">
         <f>IFERROR(LOOKUP(2,1/('Coat &amp; Skin'!$B$4:$B$203&lt;&gt;""),'Coat &amp; Skin'!$B$4:$B$203),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <f>IFERROR(LOOKUP(2,1/('Coat &amp; Skin'!$C$4:$C$203&lt;&gt;""),'Coat &amp; Skin'!$C$4:$C$203),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3">
         <f>IFERROR(LOOKUP(2,1/('Coat &amp; Skin'!$D$4:$D$203&lt;&gt;""),'Coat &amp; Skin'!$D$4:$D$203),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="3">
         <f>IFERROR(LOOKUP(2,1/('Coat &amp; Skin'!$E$4:$E$203&lt;&gt;""),'Coat &amp; Skin'!$E$4:$E$203),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <f>IFERROR(LOOKUP(2,1/('Coat &amp; Skin'!$F$4:$F$203&lt;&gt;""),'Coat &amp; Skin'!$F$4:$F$203),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" s="3">
         <f>IFERROR(LOOKUP(2,1/('Coat &amp; Skin'!$G$4:$G$203&lt;&gt;""),'Coat &amp; Skin'!$G$4:$G$203),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="3" t="str">
-        <f>'Treatment Plan'!B7</f>
-        <v>Full grooming</v>
+      <c r="A11" s="18" t="str">
+        <f ca="1"/>
+        <v>Nordic Naturals Omega 3 Pet</v>
       </c>
       <c r="B11" s="3" t="str">
-        <f>'Treatment Plan'!C7</f>
-        <v>Every 4 Weeks</v>
-      </c>
-      <c r="C11" s="4">
-        <f>'Treatment Plan'!D7</f>
-        <v>45511</v>
-      </c>
-      <c r="D11" s="4">
-        <f>'Treatment Plan'!E7</f>
-        <v>46291</v>
-      </c>
-      <c r="E11" s="4">
-        <f>'Treatment Plan'!F7</f>
-        <v>46319</v>
+        <f ca="1"/>
+        <v>Daily</v>
+      </c>
+      <c r="C11" s="17">
+        <f ca="1"/>
+        <v>46181</v>
+      </c>
+      <c r="D11" s="17">
+        <f ca="1"/>
+        <v>46302</v>
+      </c>
+      <c r="E11" s="17">
+        <f ca="1"/>
+        <v>46303</v>
       </c>
       <c r="F11" s="3" t="str">
-        <f>'Treatment Plan'!G7</f>
+        <f ca="1"/>
         <v>Active</v>
       </c>
       <c r="G11" s="3"/>
@@ -1293,12 +1349,30 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="18" t="str">
+        <f ca="1"/>
+        <v>Fluoxetine 10 MG</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <f ca="1"/>
+        <v>Daily</v>
+      </c>
+      <c r="C12" s="17">
+        <f ca="1"/>
+        <v>46181</v>
+      </c>
+      <c r="D12" s="17">
+        <f ca="1"/>
+        <v>46302</v>
+      </c>
+      <c r="E12" s="17">
+        <f ca="1"/>
+        <v>46302</v>
+      </c>
+      <c r="F12" s="3" t="str">
+        <f ca="1"/>
+        <v>Active</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -1320,177 +1394,296 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:12" ht="15">
+      <c r="A14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10" t="s">
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1">
+      <c r="A15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="B16" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!B$5:B$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4-7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!C$5:C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4-7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!D$5:D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4-7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!E$5:E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4-7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!F$5:F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4-7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
+        <v>184</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!B$5:B$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+7),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!C$5:C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+7),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!D$5:D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+7),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!E$5:E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+7),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!F$5:F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+7),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
+      <c r="C18" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!C$5:C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+14),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!D$5:D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+14),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!E$5:E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+14),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!F$5:F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+14),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
+        <v>28</v>
+      </c>
+      <c r="B19" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!B$5:B$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+7,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+14),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!C$5:C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+14,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+21),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!D$5:D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+14,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+21),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!E$5:E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+14,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+21),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!F$5:F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+14,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+21),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
+        <v>29</v>
+      </c>
+      <c r="B20" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!B$5:B$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+21,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+28),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!C$5:C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+21,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+28),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!D$5:D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+21,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+28),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!E$5:E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+21,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+28),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!F$5:F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+21,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+28),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
+        <v>30</v>
+      </c>
+      <c r="B21" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!B$5:B$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+28,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+56),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!C$5:C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+28,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+56),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!D$5:D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+28,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+56),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!E$5:E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+28,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+56),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!F$5:F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+28,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+56),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
+        <v>186</v>
+      </c>
+      <c r="B22" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!B$5:B$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+56,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+84),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!C$5:C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+56,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+84),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!D$5:D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+56,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+84),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!E$5:E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+56,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+84),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="5" t="str">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!F$5:F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+56,'Daily Check In'!$A$5:$A$404,"&lt;"&amp;'Treatment Plan'!$E$4+84),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="A23" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B23" s="14">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!B$5:B$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+84,'Daily Check In'!$A$5:$A$404,"&lt;="&amp;'Treatment Plan'!$F$4),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C23" s="16">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!C$5:C$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+84,'Daily Check In'!$A$5:$A$404,"&lt;="&amp;'Treatment Plan'!$F$4),"")</f>
+        <v>2.1818181818181817</v>
+      </c>
+      <c r="D23" s="16">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!D$5:D$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+84,'Daily Check In'!$A$5:$A$404,"&lt;="&amp;'Treatment Plan'!$F$4),"")</f>
+        <v>3.4545454545454546</v>
+      </c>
+      <c r="E23" s="16">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!E$5:E$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+84,'Daily Check In'!$A$5:$A$404,"&lt;="&amp;'Treatment Plan'!$F$4),"")</f>
+        <v>3.0909090909090908</v>
+      </c>
+      <c r="F23" s="16">
+        <f>IFERROR(AVERAGEIFS('Daily Check In'!F$5:F$404,'Daily Check In'!$A$5:$A$404,"&gt;="&amp;'Treatment Plan'!$E$4+84,'Daily Check In'!$A$5:$A$404,"&lt;="&amp;'Treatment Plan'!$F$4),"")</f>
+        <v>1.8181818181818181</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="3"/>
@@ -1506,79 +1699,18 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="8">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="G14:L14"/>
-    <mergeCell ref="G15:L22"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L28"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:L4"/>
     <mergeCell ref="G8:L8"/>
+    <mergeCell ref="G15:L23"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1586,7 +1718,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J404"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1600,63 +1732,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="4" spans="1:10" ht="30">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.5">
-      <c r="A2" s="13" t="s">
+      <c r="E4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1682,10 +1814,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1711,13 +1843,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J6" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1743,10 +1875,10 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1772,32 +1904,220 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>141</v>
+      </c>
+      <c r="I12" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1"/>
@@ -3001,7 +3321,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K203"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -3010,57 +3330,57 @@
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="30" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="72.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="72.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="3" spans="1:11" ht="15">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="K3" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3089,14 +3409,43 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="K4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1"/>
@@ -3723,7 +4072,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J303"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3731,88 +4080,110 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="8" max="8" width="18" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+    </row>
+    <row r="3" spans="1:10" ht="30">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="3" spans="1:10" ht="28">
-      <c r="A3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1">
-        <v>46291</v>
+        <v>46181</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E4" s="1">
-        <v>46291</v>
+        <v>46181</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="H4" s="1"/>
       <c r="J4" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="A5" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="1">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" t="s">
+        <v>65</v>
+      </c>
       <c r="H5" s="1"/>
+      <c r="J5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1"/>
@@ -5326,7 +5697,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H100"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
@@ -5338,91 +5709,91 @@
     <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="15">
       <c r="A1" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D2" s="1">
         <v>45992</v>
       </c>
       <c r="E2" s="1">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="F2" s="1">
         <f ca="1">TODAY()+1</f>
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1">
         <v>46013</v>
       </c>
       <c r="E3" s="1">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="F3" s="1">
         <f ca="1">TODAY()+1</f>
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D4" s="1">
         <v>46037</v>
@@ -5435,73 +5806,69 @@
         <v>46303</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D5" s="1">
         <v>46023</v>
       </c>
       <c r="E5" s="1">
-        <f ca="1">TODAY()</f>
-        <v>46294</v>
-      </c>
-      <c r="F5" s="1">
-        <f ca="1">TODAY()+1</f>
-        <v>46295</v>
-      </c>
+        <v>46180</v>
+      </c>
+      <c r="F5" s="1"/>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D6" s="1">
         <v>44531</v>
       </c>
       <c r="E6" s="1">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="F6" s="1">
         <f>EDATE(E6,1)</f>
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D7" s="1">
         <v>45511</v>
@@ -5513,21 +5880,61 @@
         <v>46319</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46181</v>
+      </c>
+      <c r="E8" s="1">
+        <f ca="1">TODAY()</f>
+        <v>46302</v>
+      </c>
+      <c r="F8" s="1">
+        <f>EDATE(E4,4)</f>
+        <v>46303</v>
+      </c>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="A9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46181</v>
+      </c>
+      <c r="E9" s="1">
+        <f ca="1">TODAY()</f>
+        <v>46302</v>
+      </c>
+      <c r="F9" s="1">
+        <f>EDATE(E5,4)</f>
+        <v>46302</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="D10" s="1"/>
@@ -6000,7 +6407,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P32"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
@@ -6013,25 +6420,25 @@
     <col min="16" max="16" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
+    <row r="1" spans="1:16" ht="20.25">
+      <c r="A1" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3"/>
@@ -6051,187 +6458,187 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" ht="15">
       <c r="A3" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3">
         <v>28</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B7" s="4">
         <v>46291</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B8" s="4">
         <f>B7+B6</f>
@@ -6239,61 +6646,61 @@
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B9" s="3">
         <v>90</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -6303,23 +6710,23 @@
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -6331,23 +6738,23 @@
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -6359,19 +6766,19 @@
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -6380,28 +6787,28 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" ht="15">
       <c r="A13" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -6415,13 +6822,13 @@
         <v>0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -6429,7 +6836,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -6443,10 +6850,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6455,7 +6862,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -6469,10 +6876,10 @@
         <v>2</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6493,10 +6900,10 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6517,10 +6924,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -6541,10 +6948,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -6560,15 +6967,15 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" ht="28.5">
       <c r="A20" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -6620,15 +7027,15 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" ht="15">
       <c r="A23" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -6649,10 +7056,10 @@
         <v>0</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -6673,10 +7080,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -6697,10 +7104,10 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -6721,10 +7128,10 @@
         <v>3</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -6745,10 +7152,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -6769,10 +7176,10 @@
         <v>5</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -6788,15 +7195,15 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="28">
+    <row r="30" spans="1:16" ht="28.5">
       <c r="A30" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
